--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487494_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487494_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1859</v>
+        <v>4.092</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2969</v>
+        <v>1.6039</v>
       </c>
       <c r="F2" t="n">
-        <v>2.8891</v>
+        <v>2.4881</v>
       </c>
       <c r="G2" t="n">
         <v>0.8621</v>
@@ -610,13 +610,13 @@
         <v>2.3502</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9737</v>
+        <v>0.8797</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4882</v>
+        <v>-0.1812</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4618</v>
+        <v>1.0609</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>M. ZORROZUA HERRERO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7363</v>
+        <v>3.4663</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8552</v>
+        <v>3.128</v>
       </c>
       <c r="F3" t="n">
-        <v>0.881</v>
+        <v>0.3382</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.6211</v>
+        <v>1.0766</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0708</v>
+        <v>-1.3334</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5502</v>
+        <v>2.4101</v>
       </c>
       <c r="J3" t="n">
-        <v>1.4622</v>
+        <v>3.0995</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2197</v>
+        <v>1.1143</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2425</v>
+        <v>1.9852</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.0833</v>
+        <v>-2.0228</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.2905</v>
+        <v>-2.4477</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.7927</v>
+        <v>0.4249</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1751</v>
+        <v>1.3709</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1543</v>
+        <v>2.3502</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5661</v>
+        <v>-0.2645</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1557</v>
+        <v>-0.2088</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4104</v>
+        <v>-0.0557</v>
       </c>
       <c r="V3" t="n">
-        <v>1.6161</v>
+        <v>1.2832</v>
       </c>
       <c r="W3" t="n">
         <v>1.2166</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3995</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ZORROZUA HERRERO</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.1722</v>
+        <v>2.606</v>
       </c>
       <c r="E4" t="n">
-        <v>3.128</v>
+        <v>1.8319</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0442</v>
+        <v>0.7741</v>
       </c>
       <c r="G4" t="n">
-        <v>1.0766</v>
+        <v>-0.6211</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3334</v>
+        <v>-0.0708</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4101</v>
+        <v>-0.5502</v>
       </c>
       <c r="J4" t="n">
-        <v>3.0995</v>
+        <v>1.4622</v>
       </c>
       <c r="K4" t="n">
-        <v>1.1143</v>
+        <v>1.2197</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9852</v>
+        <v>0.2425</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.0228</v>
+        <v>-2.0833</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.4477</v>
+        <v>-1.2905</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4249</v>
+        <v>-0.7927</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3709</v>
+        <v>1.1751</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3502</v>
+        <v>2.1543</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5586</v>
+        <v>0.4358</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2088</v>
+        <v>0.1323</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3498</v>
+        <v>0.3035</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2832</v>
+        <v>1.6161</v>
       </c>
       <c r="W4" t="n">
         <v>1.2166</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06660000000000001</v>
+        <v>0.3995</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>. SUAREZ HEVIA</t>
+          <t>R. FERNANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7359</v>
+        <v>1.7019</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1288</v>
+        <v>3.0324</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8647</v>
+        <v>-1.3305</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4327</v>
+        <v>-0.3404</v>
       </c>
       <c r="H5" t="n">
-        <v>1.5999</v>
+        <v>-3.7197</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.1672</v>
+        <v>3.3793</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9587</v>
+        <v>1.8199</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5957</v>
+        <v>-1.2709</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.637</v>
+        <v>3.0908</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5261</v>
+        <v>-2.1603</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0042</v>
+        <v>-2.4488</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5302</v>
+        <v>0.2885</v>
       </c>
       <c r="P5" t="n">
-        <v>1.7626</v>
+        <v>1.9585</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7626</v>
+        <v>1.9585</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1489</v>
+        <v>0.0172</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7546</v>
+        <v>-0.0041</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9034</v>
+        <v>0.0213</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6083</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.3329</v>
+        <v>1.2166</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>-1.15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. CUETOS FERNANDEZ</t>
+          <t>. SUAREZ HEVIA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4626</v>
+        <v>1.593</v>
       </c>
       <c r="E6" t="n">
-        <v>1.4346</v>
+        <v>0.0759</v>
       </c>
       <c r="F6" t="n">
-        <v>0.028</v>
+        <v>1.5172</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.4876</v>
+        <v>0.4327</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7857</v>
+        <v>1.5999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2981</v>
+        <v>-1.1672</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1394</v>
+        <v>0.9587</v>
       </c>
       <c r="K6" t="n">
-        <v>0.3214</v>
+        <v>1.5957</v>
       </c>
       <c r="L6" t="n">
-        <v>0.8179</v>
+        <v>-0.637</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.627</v>
+        <v>-0.5261</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.1071</v>
+        <v>0.0042</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5198</v>
+        <v>-0.5302</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3502</v>
+        <v>1.7626</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.3502</v>
+        <v>1.7626</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5334</v>
+        <v>0.006</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2952</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2381</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>0.06660000000000001</v>
+        <v>-0.6083</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06660000000000001</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ FERNANDEZ</t>
+          <t>D. CUETOS FERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.417</v>
+        <v>1.4404</v>
       </c>
       <c r="E7" t="n">
-        <v>2.8277</v>
+        <v>1.3323</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.4107</v>
+        <v>0.1081</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.3404</v>
+        <v>-1.4876</v>
       </c>
       <c r="H7" t="n">
-        <v>-3.7197</v>
+        <v>-1.7857</v>
       </c>
       <c r="I7" t="n">
-        <v>3.3793</v>
+        <v>0.2981</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8199</v>
+        <v>1.1394</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2709</v>
+        <v>0.3214</v>
       </c>
       <c r="L7" t="n">
-        <v>3.0908</v>
+        <v>0.8179</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.1603</v>
+        <v>-2.627</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.4488</v>
+        <v>-2.1071</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2885</v>
+        <v>-0.5198</v>
       </c>
       <c r="P7" t="n">
-        <v>1.9585</v>
+        <v>2.3502</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9585</v>
+        <v>2.3502</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2677</v>
+        <v>0.5112</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2088</v>
+        <v>0.1929</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0589</v>
+        <v>0.3183</v>
       </c>
       <c r="V7" t="n">
         <v>0.06660000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.15</v>
+        <v>0.06660000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8583</v>
+        <v>1.1385</v>
       </c>
       <c r="E8" t="n">
-        <v>1.502</v>
+        <v>1.809</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6437</v>
+        <v>-0.6705</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6565</v>
@@ -1078,13 +1078,13 @@
         <v>1.9585</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2904</v>
+        <v>0.5706</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1494</v>
+        <v>0.1576</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4398</v>
+        <v>0.413</v>
       </c>
       <c r="V8" t="n">
         <v>2.2244</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
+          <t>R. QUIROS HERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5682</v>
+        <v>0.423</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6603</v>
+        <v>1.5784</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0921</v>
+        <v>-1.1554</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7726</v>
+        <v>-1.5298</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1977</v>
+        <v>-1.8728</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.9703000000000001</v>
+        <v>0.343</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0393</v>
+        <v>0.3483</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.9239000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0308</v>
+        <v>1.2721</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7333</v>
+        <v>-1.8781</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2062</v>
+        <v>-0.9489</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9396</v>
+        <v>-0.9292</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1958</v>
+        <v>1.7626</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7834</v>
+        <v>1.7626</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3201</v>
+        <v>0.4655</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4623</v>
+        <v>0.0135</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1422</v>
+        <v>0.452</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2166</v>
+        <v>-0.2754</v>
       </c>
       <c r="W9" t="n">
         <v>1.2166</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R. QUIROS HERNANDEZ</t>
+          <t>N. LOPEZ ALVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2718</v>
+        <v>0.2658</v>
       </c>
       <c r="E10" t="n">
-        <v>1.3737</v>
+        <v>0.251</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1019</v>
+        <v>0.0148</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5298</v>
+        <v>-0.7726</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8728</v>
+        <v>0.1977</v>
       </c>
       <c r="I10" t="n">
-        <v>0.343</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.3483</v>
+        <v>-0.0393</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.9239000000000001</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2721</v>
+        <v>-0.0308</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.8781</v>
+        <v>-0.7333</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.9489</v>
+        <v>0.2062</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9292</v>
+        <v>-0.9396</v>
       </c>
       <c r="P10" t="n">
-        <v>1.7626</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R10" t="n">
-        <v>1.7626</v>
+        <v>0.7834</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3143</v>
+        <v>0.0176</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1911</v>
+        <v>0.0529</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5054</v>
+        <v>-0.0353</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.2754</v>
+        <v>1.2166</v>
       </c>
       <c r="W10" t="n">
         <v>1.2166</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9531</v>
+        <v>-1.2719</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8571</v>
+        <v>-1.5501</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.096</v>
+        <v>0.2782</v>
       </c>
       <c r="G11" t="n">
         <v>0.1364</v>
@@ -1312,13 +1312,13 @@
         <v>2.1543</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.3061</v>
+        <v>-0.6249</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9328</v>
+        <v>-0.6258</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3733</v>
+        <v>0.0009</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>15.4551</v>
+        <v>15.455</v>
       </c>
       <c r="E12" t="n">
-        <v>13.0925</v>
+        <v>13.0927</v>
       </c>
       <c r="F12" t="n">
-        <v>2.3626</v>
+        <v>2.362300000000001</v>
       </c>
       <c r="G12" t="n">
         <v>-3.9002</v>
@@ -1369,7 +1369,7 @@
         <v>6.0881</v>
       </c>
       <c r="L12" t="n">
-        <v>6.4589</v>
+        <v>6.458900000000002</v>
       </c>
       <c r="M12" t="n">
         <v>-16.4474</v>
@@ -1378,7 +1378,7 @@
         <v>-11.8793</v>
       </c>
       <c r="O12" t="n">
-        <v>-4.568</v>
+        <v>-4.568000000000001</v>
       </c>
       <c r="P12" t="n">
         <v>11.7509</v>
@@ -1390,22 +1390,22 @@
         <v>19.5848</v>
       </c>
       <c r="S12" t="n">
-        <v>2.014500000000001</v>
+        <v>2.0142</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0205</v>
+        <v>-1.0206</v>
       </c>
       <c r="U12" t="n">
-        <v>3.0347</v>
+        <v>3.0348</v>
       </c>
       <c r="V12" t="n">
-        <v>5.589799999999999</v>
+        <v>5.5898</v>
       </c>
       <c r="W12" t="n">
         <v>9.399899999999999</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.810099999999999</v>
+        <v>-3.8101</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.2252</v>
+        <v>5.065</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1807</v>
+        <v>5.59</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9555</v>
+        <v>-0.525</v>
       </c>
       <c r="G13" t="n">
         <v>3.9805</v>
@@ -1468,13 +1468,13 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.4478</v>
+        <v>-0.608</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1704</v>
+        <v>-0.7611</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2774</v>
+        <v>0.1531</v>
       </c>
       <c r="V13" t="n">
         <v>3.2593</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1821</v>
+        <v>0.2356</v>
       </c>
       <c r="E14" t="n">
         <v>-0.0546</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2367</v>
+        <v>0.2901</v>
       </c>
       <c r="G14" t="n">
         <v>0.2829</v>
@@ -1546,13 +1546,13 @@
         <v>0.1958</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2967</v>
+        <v>-0.2432</v>
       </c>
       <c r="T14" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2373</v>
+        <v>-0.1838</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.317</v>
+        <v>-0.0275</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.4365</v>
+        <v>-0.3342</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1196</v>
+        <v>0.3067</v>
       </c>
       <c r="G15" t="n">
         <v>1.5168</v>
@@ -1624,13 +1624,13 @@
         <v>0.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.267</v>
+        <v>0.0225</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1482</v>
+        <v>0.039</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. AÑON DOSIL</t>
+          <t>A. CORBACHO DE LA CRUZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9316</v>
+        <v>-0.7074</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8267</v>
+        <v>-0.8588</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.7583</v>
+        <v>0.1513</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0858</v>
+        <v>-0.7683</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1099</v>
+        <v>-1.1724</v>
       </c>
       <c r="I16" t="n">
-        <v>1.9759</v>
+        <v>0.4042</v>
       </c>
       <c r="J16" t="n">
-        <v>4.8754</v>
+        <v>0.8921</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7182</v>
+        <v>0.3879</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1572</v>
+        <v>0.5043</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7896</v>
+        <v>-1.6604</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6083</v>
+        <v>-1.5603</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.1813</v>
+        <v>-0.1001</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.9377</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.917</v>
+        <v>-0.9792</v>
       </c>
       <c r="R16" t="n">
         <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.196</v>
+        <v>0.3938</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1317</v>
+        <v>-0.4388</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0643</v>
+        <v>0.8325</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.8837</v>
+        <v>-0.3329</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>-0.3329</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8837</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. CORBACHO DE LA CRUZ</t>
+          <t>A. AÑON DOSIL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0587</v>
+        <v>-0.8616</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.3705</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3117</v>
+        <v>-1.3813</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.7683</v>
+        <v>3.0858</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.1724</v>
+        <v>1.1099</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4042</v>
+        <v>1.9759</v>
       </c>
       <c r="J17" t="n">
-        <v>0.8921</v>
+        <v>4.8754</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3879</v>
+        <v>1.7182</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5043</v>
+        <v>3.1572</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.6604</v>
+        <v>-1.7896</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5603</v>
+        <v>-0.6083</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.1001</v>
+        <v>-1.1813</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-2.9377</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9792</v>
+        <v>-3.917</v>
       </c>
       <c r="R17" t="n">
         <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0425</v>
+        <v>-0.126</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9504</v>
+        <v>-0.4388</v>
       </c>
       <c r="U17" t="n">
-        <v>0.9929</v>
+        <v>0.3127</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3329</v>
+        <v>-0.8837</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3329</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.8837</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.1151</v>
+        <v>-1.0524</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0546</v>
+        <v>-0.1501</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1696</v>
+        <v>-0.9023</v>
       </c>
       <c r="G18" t="n">
         <v>-0.094</v>
@@ -1858,13 +1858,13 @@
         <v>0.3917</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4335</v>
+        <v>-0.3708</v>
       </c>
       <c r="T18" t="n">
-        <v>0.207</v>
+        <v>0.0023</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6405</v>
+        <v>-0.3732</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9687</v>
+        <v>-2.33</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.4757</v>
+        <v>-0.1687</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.493</v>
+        <v>-2.1613</v>
       </c>
       <c r="G19" t="n">
         <v>1.2529</v>
@@ -1936,13 +1936,13 @@
         <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0491</v>
+        <v>-0.3121</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.9504</v>
+        <v>-0.6434</v>
       </c>
       <c r="U19" t="n">
-        <v>0.9995000000000001</v>
+        <v>0.3313</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3329</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.039</v>
+        <v>-3.8862</v>
       </c>
       <c r="E20" t="n">
-        <v>0.8539</v>
+        <v>0.1376</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.8929</v>
+        <v>-4.0238</v>
       </c>
       <c r="G20" t="n">
         <v>1.3346</v>
@@ -2014,13 +2014,13 @@
         <v>0.5875</v>
       </c>
       <c r="S20" t="n">
-        <v>1.8638</v>
+        <v>1.0166</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9663</v>
+        <v>0.25</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8975</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="V20" t="n">
         <v>-4.8664</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9808</v>
+        <v>-5.0758</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.1077</v>
+        <v>-3.3124</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.8731</v>
+        <v>-1.7634</v>
       </c>
       <c r="G21" t="n">
         <v>-1.0465</v>
@@ -2092,13 +2092,13 @@
         <v>1.5668</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.1302</v>
+        <v>-0.2251</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3694</v>
+        <v>-0.574</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2392</v>
+        <v>0.3489</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4332</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.4514</v>
+        <v>-6.1325</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.8333</v>
+        <v>-3.731</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6181</v>
+        <v>-2.4015</v>
       </c>
       <c r="G22" t="n">
         <v>-5.6445</v>
@@ -2170,13 +2170,13 @@
         <v>0.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.1987</v>
+        <v>-0.8797</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4576</v>
+        <v>-0.3552</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7411</v>
+        <v>-0.5245</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-15.455</v>
+        <v>-14.7728</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3624</v>
+        <v>-2.3625</v>
       </c>
       <c r="F23" t="n">
-        <v>-13.0925</v>
+        <v>-12.4105</v>
       </c>
       <c r="G23" t="n">
         <v>3.900200000000001</v>
@@ -2227,7 +2227,7 @@
         <v>11.8794</v>
       </c>
       <c r="L23" t="n">
-        <v>4.568099999999999</v>
+        <v>4.568100000000001</v>
       </c>
       <c r="M23" t="n">
         <v>-12.5471</v>
@@ -2248,13 +2248,13 @@
         <v>7.833699999999999</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.0145</v>
+        <v>-1.332</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.0348</v>
+        <v>-3.0349</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0203</v>
+        <v>1.7026</v>
       </c>
       <c r="V23" t="n">
         <v>-5.589799999999999</v>
